--- a/12602999.xlsx
+++ b/12602999.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -253,6 +253,27 @@
   </si>
   <si>
     <t>Sunday spent at home with family</t>
+  </si>
+  <si>
+    <t>travelled from home and came directly to college selp less and rested after returning</t>
+  </si>
+  <si>
+    <t>long college day with many classes</t>
+  </si>
+  <si>
+    <t>attanded classes ad complete regular work</t>
+  </si>
+  <si>
+    <t>weekendrelexed and completed personal work</t>
+  </si>
+  <si>
+    <t>relexed Sunday and spent time on personal work</t>
+  </si>
+  <si>
+    <t>busy college day</t>
+  </si>
+  <si>
+    <t>shorter college day</t>
   </si>
 </sst>
 </file>
@@ -1608,220 +1629,442 @@
         <v>73</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
-      <c r="A19" s="8"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="10" t="str">
+    <row r="19" spans="1:14" ht="60">
+      <c r="A19" s="8">
+        <v>46265</v>
+      </c>
+      <c r="B19" s="9">
+        <v>300</v>
+      </c>
+      <c r="C19" s="9">
+        <v>120</v>
+      </c>
+      <c r="D19" s="9">
+        <v>20</v>
+      </c>
+      <c r="E19" s="9">
+        <v>0</v>
+      </c>
+      <c r="F19" s="9">
+        <v>200</v>
+      </c>
+      <c r="G19" s="9">
+        <v>4</v>
+      </c>
+      <c r="H19" s="9">
+        <v>120</v>
+      </c>
+      <c r="I19" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="10" t="str">
+        <v>760</v>
+      </c>
+      <c r="J19" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="12"/>
+        <v>680</v>
+      </c>
+      <c r="K19" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="L19" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M19" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="N19" s="12" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="20" spans="1:14">
-      <c r="A20" s="8"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="10" t="str">
+      <c r="A20" s="8">
+        <v>46266</v>
+      </c>
+      <c r="B20" s="9">
+        <v>450</v>
+      </c>
+      <c r="C20" s="9">
+        <v>60</v>
+      </c>
+      <c r="D20" s="9">
+        <v>0</v>
+      </c>
+      <c r="E20" s="9">
+        <v>40</v>
+      </c>
+      <c r="F20" s="9">
+        <v>150</v>
+      </c>
+      <c r="G20" s="9">
+        <v>3</v>
+      </c>
+      <c r="H20" s="9">
+        <v>180</v>
+      </c>
+      <c r="I20" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="10" t="str">
+        <v>880</v>
+      </c>
+      <c r="J20" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="11"/>
-      <c r="N20" s="12"/>
-    </row>
-    <row r="21" spans="1:14">
-      <c r="A21" s="8"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="10" t="str">
+        <v>560</v>
+      </c>
+      <c r="K20" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L20" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M20" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N20" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="30">
+      <c r="A21" s="8">
+        <v>46267</v>
+      </c>
+      <c r="B21" s="9">
+        <v>480</v>
+      </c>
+      <c r="C21" s="9">
+        <v>50</v>
+      </c>
+      <c r="D21" s="9">
+        <v>160</v>
+      </c>
+      <c r="E21" s="9">
+        <v>40</v>
+      </c>
+      <c r="F21" s="9">
+        <v>400</v>
+      </c>
+      <c r="G21" s="9">
+        <v>8</v>
+      </c>
+      <c r="H21" s="9">
+        <v>90</v>
+      </c>
+      <c r="I21" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="10" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J21" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="11"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="11"/>
-      <c r="N21" s="12"/>
+        <v>220</v>
+      </c>
+      <c r="K21" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="L21" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M21" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="N21" s="12" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="22" spans="1:14">
-      <c r="A22" s="8"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="10" t="str">
+      <c r="A22" s="8">
+        <v>46268</v>
+      </c>
+      <c r="B22" s="9">
+        <v>510</v>
+      </c>
+      <c r="C22" s="9">
+        <v>80</v>
+      </c>
+      <c r="D22" s="9">
+        <v>60</v>
+      </c>
+      <c r="E22" s="9">
+        <v>0</v>
+      </c>
+      <c r="F22" s="9">
+        <v>250</v>
+      </c>
+      <c r="G22" s="9">
+        <v>5</v>
+      </c>
+      <c r="H22" s="9">
+        <v>100</v>
+      </c>
+      <c r="I22" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="10" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J22" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="11"/>
-      <c r="N22" s="12"/>
-    </row>
-    <row r="23" spans="1:14">
-      <c r="A23" s="8"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="10" t="str">
+        <v>440</v>
+      </c>
+      <c r="K22" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L22" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M22" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N22" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="30">
+      <c r="A23" s="8">
+        <v>46269</v>
+      </c>
+      <c r="B23" s="9">
+        <v>450</v>
+      </c>
+      <c r="C23" s="9">
+        <v>70</v>
+      </c>
+      <c r="D23" s="9">
+        <v>40</v>
+      </c>
+      <c r="E23" s="9">
+        <v>80</v>
+      </c>
+      <c r="F23" s="9">
+        <v>250</v>
+      </c>
+      <c r="G23" s="9">
+        <v>5</v>
+      </c>
+      <c r="H23" s="9">
+        <v>55</v>
+      </c>
+      <c r="I23" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="10" t="str">
+        <v>945</v>
+      </c>
+      <c r="J23" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="11"/>
-      <c r="N23" s="12"/>
-    </row>
-    <row r="24" spans="1:14">
-      <c r="A24" s="8"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="10" t="str">
+        <v>495</v>
+      </c>
+      <c r="K23" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L23" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M23" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N23" s="12" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="30">
+      <c r="A24" s="8">
+        <v>46270</v>
+      </c>
+      <c r="B24" s="9">
+        <v>720</v>
+      </c>
+      <c r="C24" s="9">
+        <v>20</v>
+      </c>
+      <c r="D24" s="9">
+        <v>270</v>
+      </c>
+      <c r="E24" s="9">
+        <v>0</v>
+      </c>
+      <c r="F24" s="9">
+        <v>0</v>
+      </c>
+      <c r="G24" s="9">
+        <v>0</v>
+      </c>
+      <c r="H24" s="9">
+        <v>240</v>
+      </c>
+      <c r="I24" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="10" t="str">
+        <v>1250</v>
+      </c>
+      <c r="J24" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="11"/>
-      <c r="N24" s="12"/>
-    </row>
-    <row r="25" spans="1:14">
-      <c r="A25" s="8"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="10" t="str">
+        <v>190</v>
+      </c>
+      <c r="K24" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L24" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M24" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="N24" s="12" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="30">
+      <c r="A25" s="8">
+        <v>46271</v>
+      </c>
+      <c r="B25" s="9">
+        <v>690</v>
+      </c>
+      <c r="C25" s="9">
+        <v>20</v>
+      </c>
+      <c r="D25" s="9">
+        <v>200</v>
+      </c>
+      <c r="E25" s="9">
+        <v>0</v>
+      </c>
+      <c r="F25" s="9">
+        <v>0</v>
+      </c>
+      <c r="G25" s="9">
+        <v>0</v>
+      </c>
+      <c r="H25" s="9">
+        <v>180</v>
+      </c>
+      <c r="I25" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="10" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J25" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="11"/>
-      <c r="N25" s="12"/>
+        <v>350</v>
+      </c>
+      <c r="K25" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L25" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M25" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N25" s="12" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="26" spans="1:14">
-      <c r="A26" s="8"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="10" t="str">
+      <c r="A26" s="8">
+        <v>46272</v>
+      </c>
+      <c r="B26" s="9">
+        <v>480</v>
+      </c>
+      <c r="C26" s="9">
+        <v>70</v>
+      </c>
+      <c r="D26" s="9">
+        <v>80</v>
+      </c>
+      <c r="E26" s="9">
+        <v>60</v>
+      </c>
+      <c r="F26" s="9">
+        <v>300</v>
+      </c>
+      <c r="G26" s="9">
+        <v>6</v>
+      </c>
+      <c r="H26" s="9">
+        <v>135</v>
+      </c>
+      <c r="I26" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="10" t="str">
+        <v>1125</v>
+      </c>
+      <c r="J26" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="11"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="11"/>
-      <c r="N26" s="12"/>
+        <v>315</v>
+      </c>
+      <c r="K26" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L26" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M26" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N26" s="12" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="27" spans="1:14">
-      <c r="A27" s="8"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="10" t="str">
+      <c r="A27" s="8">
+        <v>46273</v>
+      </c>
+      <c r="B27" s="9">
+        <v>550</v>
+      </c>
+      <c r="C27" s="9">
+        <v>40</v>
+      </c>
+      <c r="D27" s="9">
+        <v>120</v>
+      </c>
+      <c r="E27" s="9">
+        <v>0</v>
+      </c>
+      <c r="F27" s="9">
+        <v>100</v>
+      </c>
+      <c r="G27" s="9">
+        <v>2</v>
+      </c>
+      <c r="H27" s="9">
+        <v>160</v>
+      </c>
+      <c r="I27" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="10" t="str">
+        <v>970</v>
+      </c>
+      <c r="J27" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="11"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="11"/>
-      <c r="N27" s="12"/>
+        <v>470</v>
+      </c>
+      <c r="K27" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L27" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M27" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N27" s="12" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="28" spans="1:14">
-      <c r="A28" s="8"/>
+      <c r="A28" s="8">
+        <v>46274</v>
+      </c>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
+      <c r="F28" s="9">
+        <v>400</v>
+      </c>
+      <c r="G28" s="9">
+        <v>8</v>
+      </c>
       <c r="H28" s="9"/>
-      <c r="I28" s="10" t="str">
+      <c r="I28" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="10" t="str">
+        <v>400</v>
+      </c>
+      <c r="J28" s="10">
         <f t="shared" si="1"/>
-        <v/>
+        <v>1040</v>
       </c>
       <c r="K28" s="11"/>
       <c r="L28" s="11"/>

--- a/12602999.xlsx
+++ b/12602999.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -274,6 +274,9 @@
   </si>
   <si>
     <t>shorter college day</t>
+  </si>
+  <si>
+    <t>long college day with 8 classes</t>
   </si>
 </sst>
 </file>
@@ -2043,33 +2046,51 @@
         <v>80</v>
       </c>
     </row>
-    <row r="28" spans="1:14">
+    <row r="28" spans="1:14" ht="30">
       <c r="A28" s="8">
         <v>46274</v>
       </c>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
+      <c r="B28" s="9">
+        <v>480</v>
+      </c>
+      <c r="C28" s="9">
+        <v>80</v>
+      </c>
+      <c r="D28" s="9">
+        <v>50</v>
+      </c>
+      <c r="E28" s="9">
+        <v>40</v>
+      </c>
       <c r="F28" s="9">
         <v>400</v>
       </c>
       <c r="G28" s="9">
         <v>8</v>
       </c>
-      <c r="H28" s="9"/>
+      <c r="H28" s="9">
+        <v>90</v>
+      </c>
       <c r="I28" s="10">
         <f t="shared" si="0"/>
-        <v>400</v>
+        <v>1140</v>
       </c>
       <c r="J28" s="10">
         <f t="shared" si="1"/>
-        <v>1040</v>
-      </c>
-      <c r="K28" s="11"/>
-      <c r="L28" s="11"/>
-      <c r="M28" s="11"/>
-      <c r="N28" s="12"/>
+        <v>300</v>
+      </c>
+      <c r="K28" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="L28" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M28" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="N28" s="12" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="8"/>

--- a/12602999.xlsx
+++ b/12602999.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -277,6 +277,12 @@
   </si>
   <si>
     <t>long college day with 8 classes</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>attanded 3 classes and enjoy fresher party with friends</t>
   </si>
 </sst>
 </file>
@@ -2092,27 +2098,51 @@
         <v>81</v>
       </c>
     </row>
-    <row r="29" spans="1:14">
-      <c r="A29" s="8"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="10" t="str">
+    <row r="29" spans="1:14" ht="30">
+      <c r="A29" s="8">
+        <v>46275</v>
+      </c>
+      <c r="B29" s="9">
+        <v>480</v>
+      </c>
+      <c r="C29" s="9">
+        <v>60</v>
+      </c>
+      <c r="D29" s="9">
+        <v>0</v>
+      </c>
+      <c r="E29" s="9">
+        <v>0</v>
+      </c>
+      <c r="F29" s="9">
+        <v>150</v>
+      </c>
+      <c r="G29" s="9">
+        <v>3</v>
+      </c>
+      <c r="H29" s="9">
+        <v>330</v>
+      </c>
+      <c r="I29" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="10" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J29" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="11"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="11"/>
-      <c r="N29" s="12"/>
+        <v>420</v>
+      </c>
+      <c r="K29" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="L29" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="M29" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="N29" s="12" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="8"/>

--- a/12602999.xlsx
+++ b/12602999.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -283,6 +283,12 @@
   </si>
   <si>
     <t>attanded 3 classes and enjoy fresher party with friends</t>
+  </si>
+  <si>
+    <t>relex weekend</t>
+  </si>
+  <si>
+    <t>attand regular classes and travelled to home</t>
   </si>
 </sst>
 </file>
@@ -2144,49 +2150,97 @@
         <v>83</v>
       </c>
     </row>
-    <row r="30" spans="1:14">
-      <c r="A30" s="8"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="10" t="str">
+    <row r="30" spans="1:14" ht="30">
+      <c r="A30" s="8">
+        <v>46276</v>
+      </c>
+      <c r="B30" s="9">
+        <v>470</v>
+      </c>
+      <c r="C30" s="9">
+        <v>100</v>
+      </c>
+      <c r="D30" s="9">
+        <v>0</v>
+      </c>
+      <c r="E30" s="9">
+        <v>50</v>
+      </c>
+      <c r="F30" s="9">
+        <v>150</v>
+      </c>
+      <c r="G30" s="9">
+        <v>3</v>
+      </c>
+      <c r="H30" s="9">
+        <v>350</v>
+      </c>
+      <c r="I30" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="10" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J30" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="11"/>
-      <c r="L30" s="11"/>
-      <c r="M30" s="11"/>
-      <c r="N30" s="12"/>
+        <v>320</v>
+      </c>
+      <c r="K30" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L30" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M30" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N30" s="12" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="31" spans="1:14">
-      <c r="A31" s="8"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="10" t="str">
+      <c r="A31" s="8">
+        <v>46277</v>
+      </c>
+      <c r="B31" s="9">
+        <v>550</v>
+      </c>
+      <c r="C31" s="9">
+        <v>80</v>
+      </c>
+      <c r="D31" s="9">
+        <v>0</v>
+      </c>
+      <c r="E31" s="9">
+        <v>80</v>
+      </c>
+      <c r="F31" s="9">
+        <v>0</v>
+      </c>
+      <c r="G31" s="9">
+        <v>0</v>
+      </c>
+      <c r="H31" s="9">
+        <v>450</v>
+      </c>
+      <c r="I31" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="10" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J31" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="11"/>
-      <c r="L31" s="11"/>
-      <c r="M31" s="11"/>
-      <c r="N31" s="12"/>
+        <v>280</v>
+      </c>
+      <c r="K31" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L31" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M31" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N31" s="12" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="8"/>

--- a/12602999.xlsx
+++ b/12602999.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -285,10 +285,16 @@
     <t>attanded 3 classes and enjoy fresher party with friends</t>
   </si>
   <si>
-    <t>relex weekend</t>
+    <t>attand regular classes and travelled to home</t>
   </si>
   <si>
-    <t>attand regular classes and travelled to home</t>
+    <t>relex weekend at home</t>
+  </si>
+  <si>
+    <t>travelled back from home and cleaned the room</t>
+  </si>
+  <si>
+    <t>o</t>
   </si>
 </sst>
 </file>
@@ -2193,7 +2199,7 @@
         <v>51</v>
       </c>
       <c r="N30" s="12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -2239,30 +2245,54 @@
         <v>51</v>
       </c>
       <c r="N31" s="12" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14">
-      <c r="A32" s="8"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="10" t="str">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="30">
+      <c r="A32" s="8">
+        <v>46278</v>
+      </c>
+      <c r="B32" s="9">
+        <v>660</v>
+      </c>
+      <c r="C32" s="9">
+        <v>90</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="E32" s="9">
+        <v>0</v>
+      </c>
+      <c r="F32" s="9">
+        <v>0</v>
+      </c>
+      <c r="G32" s="9">
+        <v>0</v>
+      </c>
+      <c r="H32" s="9">
+        <v>300</v>
+      </c>
+      <c r="I32" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="10" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J32" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="11"/>
-      <c r="L32" s="11"/>
-      <c r="M32" s="11"/>
-      <c r="N32" s="12"/>
+        <v>390</v>
+      </c>
+      <c r="K32" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L32" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M32" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N32" s="12" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="8"/>

--- a/12602999.xlsx
+++ b/12602999.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -294,7 +294,7 @@
     <t>travelled back from home and cleaned the room</t>
   </si>
   <si>
-    <t>o</t>
+    <t>attend 6 classes and complete regular activities</t>
   </si>
 </sst>
 </file>
@@ -2258,8 +2258,8 @@
       <c r="C32" s="9">
         <v>90</v>
       </c>
-      <c r="D32" s="9" t="s">
-        <v>87</v>
+      <c r="D32" s="9">
+        <v>0</v>
       </c>
       <c r="E32" s="9">
         <v>0</v>
@@ -2294,27 +2294,51 @@
         <v>86</v>
       </c>
     </row>
-    <row r="33" spans="1:14">
-      <c r="A33" s="8"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="10" t="str">
+    <row r="33" spans="1:14" ht="30">
+      <c r="A33" s="8">
+        <v>46279</v>
+      </c>
+      <c r="B33" s="9">
+        <v>500</v>
+      </c>
+      <c r="C33" s="9">
+        <v>60</v>
+      </c>
+      <c r="D33" s="9">
+        <v>0</v>
+      </c>
+      <c r="E33" s="9">
+        <v>0</v>
+      </c>
+      <c r="F33" s="9">
+        <v>300</v>
+      </c>
+      <c r="G33" s="9">
+        <v>6</v>
+      </c>
+      <c r="H33" s="9">
+        <v>120</v>
+      </c>
+      <c r="I33" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="10" t="str">
+        <v>980</v>
+      </c>
+      <c r="J33" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="11"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="11"/>
-      <c r="N33" s="12"/>
+        <v>460</v>
+      </c>
+      <c r="K33" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L33" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M33" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="N33" s="12" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" s="8"/>

--- a/12602999.xlsx
+++ b/12602999.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -295,6 +295,9 @@
   </si>
   <si>
     <t>attend 6 classes and complete regular activities</t>
+  </si>
+  <si>
+    <t>regular college day with 3 classes</t>
   </si>
 </sst>
 </file>
@@ -2340,27 +2343,51 @@
         <v>87</v>
       </c>
     </row>
-    <row r="34" spans="1:14">
-      <c r="A34" s="8"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="10" t="str">
+    <row r="34" spans="1:14" ht="30">
+      <c r="A34" s="8">
+        <v>46280</v>
+      </c>
+      <c r="B34" s="9">
+        <v>450</v>
+      </c>
+      <c r="C34" s="9">
+        <v>80</v>
+      </c>
+      <c r="D34" s="9">
+        <v>60</v>
+      </c>
+      <c r="E34" s="9">
+        <v>0</v>
+      </c>
+      <c r="F34" s="9">
+        <v>150</v>
+      </c>
+      <c r="G34" s="9">
+        <v>3</v>
+      </c>
+      <c r="H34" s="9">
+        <v>120</v>
+      </c>
+      <c r="I34" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="10" t="str">
+        <v>860</v>
+      </c>
+      <c r="J34" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="11"/>
-      <c r="L34" s="11"/>
-      <c r="M34" s="11"/>
-      <c r="N34" s="12"/>
+        <v>580</v>
+      </c>
+      <c r="K34" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L34" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M34" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N34" s="12" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="35" spans="1:14">
       <c r="A35" s="8"/>

--- a/12602999.xlsx
+++ b/12602999.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -298,6 +298,9 @@
   </si>
   <si>
     <t>regular college day with 3 classes</t>
+  </si>
+  <si>
+    <t>long college day with 8 classes felt tierd afterward</t>
   </si>
 </sst>
 </file>
@@ -2389,27 +2392,51 @@
         <v>88</v>
       </c>
     </row>
-    <row r="35" spans="1:14">
-      <c r="A35" s="8"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="10" t="str">
+    <row r="35" spans="1:14" ht="30">
+      <c r="A35" s="8">
+        <v>46281</v>
+      </c>
+      <c r="B35" s="9">
+        <v>479</v>
+      </c>
+      <c r="C35" s="9">
+        <v>80</v>
+      </c>
+      <c r="D35" s="9">
+        <v>60</v>
+      </c>
+      <c r="E35" s="9">
+        <v>40</v>
+      </c>
+      <c r="F35" s="9">
+        <v>400</v>
+      </c>
+      <c r="G35" s="9">
+        <v>8</v>
+      </c>
+      <c r="H35" s="9">
+        <v>90</v>
+      </c>
+      <c r="I35" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="10" t="str">
+        <v>1149</v>
+      </c>
+      <c r="J35" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="11"/>
-      <c r="L35" s="11"/>
-      <c r="M35" s="11"/>
-      <c r="N35" s="12"/>
+        <v>291</v>
+      </c>
+      <c r="K35" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="L35" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M35" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="N35" s="12" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="8"/>

--- a/12602999.xlsx
+++ b/12602999.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="91">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -301,6 +301,9 @@
   </si>
   <si>
     <t>long college day with 8 classes felt tierd afterward</t>
+  </si>
+  <si>
+    <t>regular day with 5 classes</t>
   </si>
 </sst>
 </file>
@@ -2439,26 +2442,50 @@
       </c>
     </row>
     <row r="36" spans="1:14">
-      <c r="A36" s="8"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="10" t="str">
+      <c r="A36" s="8">
+        <v>46282</v>
+      </c>
+      <c r="B36" s="9">
+        <v>500</v>
+      </c>
+      <c r="C36" s="9">
+        <v>100</v>
+      </c>
+      <c r="D36" s="9">
+        <v>60</v>
+      </c>
+      <c r="E36" s="9">
+        <v>0</v>
+      </c>
+      <c r="F36" s="9">
+        <v>250</v>
+      </c>
+      <c r="G36" s="9">
+        <v>5</v>
+      </c>
+      <c r="H36" s="9">
+        <v>120</v>
+      </c>
+      <c r="I36" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="10" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J36" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="11"/>
-      <c r="L36" s="11"/>
-      <c r="M36" s="11"/>
-      <c r="N36" s="12"/>
+        <v>410</v>
+      </c>
+      <c r="K36" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L36" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M36" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N36" s="12" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" s="8"/>

--- a/12602999.xlsx
+++ b/12602999.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="95">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -304,6 +304,18 @@
   </si>
   <si>
     <t>regular day with 5 classes</t>
+  </si>
+  <si>
+    <t>Stressed</t>
+  </si>
+  <si>
+    <t>regular college day with 5 classes</t>
+  </si>
+  <si>
+    <t>went to college for ca and completed the test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">relexed Sunday and prepared for the next ca </t>
   </si>
 </sst>
 </file>
@@ -2487,71 +2499,143 @@
         <v>90</v>
       </c>
     </row>
-    <row r="37" spans="1:14">
-      <c r="A37" s="8"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
-      <c r="I37" s="10" t="str">
+    <row r="37" spans="1:14" ht="30">
+      <c r="A37" s="8">
+        <v>46283</v>
+      </c>
+      <c r="B37" s="9">
+        <v>450</v>
+      </c>
+      <c r="C37" s="9">
+        <v>80</v>
+      </c>
+      <c r="D37" s="9">
+        <v>120</v>
+      </c>
+      <c r="E37" s="9">
+        <v>50</v>
+      </c>
+      <c r="F37" s="9">
+        <v>250</v>
+      </c>
+      <c r="G37" s="9">
+        <v>5</v>
+      </c>
+      <c r="H37" s="9">
+        <v>100</v>
+      </c>
+      <c r="I37" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="10" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J37" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="11"/>
-      <c r="L37" s="11"/>
-      <c r="M37" s="11"/>
-      <c r="N37" s="12"/>
-    </row>
-    <row r="38" spans="1:14">
-      <c r="A38" s="8"/>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="9"/>
-      <c r="I38" s="10" t="str">
+        <v>390</v>
+      </c>
+      <c r="K37" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L37" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M37" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N37" s="12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="30">
+      <c r="A38" s="8">
+        <v>46284</v>
+      </c>
+      <c r="B38" s="9">
+        <v>500</v>
+      </c>
+      <c r="C38" s="9">
+        <v>80</v>
+      </c>
+      <c r="D38" s="9">
+        <v>0</v>
+      </c>
+      <c r="E38" s="9">
+        <v>0</v>
+      </c>
+      <c r="F38" s="9">
+        <v>0</v>
+      </c>
+      <c r="G38" s="9">
+        <v>0</v>
+      </c>
+      <c r="H38" s="9">
+        <v>120</v>
+      </c>
+      <c r="I38" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="10" t="str">
+        <v>700</v>
+      </c>
+      <c r="J38" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="11"/>
-      <c r="L38" s="11"/>
-      <c r="M38" s="11"/>
-      <c r="N38" s="12"/>
-    </row>
-    <row r="39" spans="1:14">
-      <c r="A39" s="8"/>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
-      <c r="H39" s="9"/>
-      <c r="I39" s="10" t="str">
+        <v>740</v>
+      </c>
+      <c r="K38" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="L38" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M38" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N38" s="12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="30">
+      <c r="A39" s="8">
+        <v>46285</v>
+      </c>
+      <c r="B39" s="9">
+        <v>600</v>
+      </c>
+      <c r="C39" s="9">
+        <v>60</v>
+      </c>
+      <c r="D39" s="9">
+        <v>220</v>
+      </c>
+      <c r="E39" s="9">
+        <v>0</v>
+      </c>
+      <c r="F39" s="9">
+        <v>0</v>
+      </c>
+      <c r="G39" s="9">
+        <v>0</v>
+      </c>
+      <c r="H39" s="9">
+        <v>300</v>
+      </c>
+      <c r="I39" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="10" t="str">
+        <v>1180</v>
+      </c>
+      <c r="J39" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="11"/>
-      <c r="L39" s="11"/>
-      <c r="M39" s="11"/>
-      <c r="N39" s="12"/>
+        <v>260</v>
+      </c>
+      <c r="K39" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="L39" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M39" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N39" s="12" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="8"/>

--- a/12602999.xlsx
+++ b/12602999.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="96">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -316,6 +316,9 @@
   </si>
   <si>
     <t xml:space="preserve">relexed Sunday and prepared for the next ca </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> attended regular classes and participated in an active listening workshop </t>
   </si>
 </sst>
 </file>
@@ -2637,27 +2640,51 @@
         <v>94</v>
       </c>
     </row>
-    <row r="40" spans="1:14">
-      <c r="A40" s="8"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="9"/>
-      <c r="I40" s="10" t="str">
+    <row r="40" spans="1:14" ht="45">
+      <c r="A40" s="8">
+        <v>46286</v>
+      </c>
+      <c r="B40" s="9">
+        <v>500</v>
+      </c>
+      <c r="C40" s="9">
+        <v>60</v>
+      </c>
+      <c r="D40" s="9">
+        <v>150</v>
+      </c>
+      <c r="E40" s="9">
+        <v>0</v>
+      </c>
+      <c r="F40" s="9">
+        <v>300</v>
+      </c>
+      <c r="G40" s="9">
+        <v>5</v>
+      </c>
+      <c r="H40" s="9">
+        <v>30</v>
+      </c>
+      <c r="I40" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="10" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J40" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="11"/>
-      <c r="L40" s="11"/>
-      <c r="M40" s="11"/>
-      <c r="N40" s="12"/>
+        <v>400</v>
+      </c>
+      <c r="K40" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="L40" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M40" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N40" s="12" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="8"/>

--- a/12602999.xlsx
+++ b/12602999.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -253,24 +253,6 @@
   </si>
   <si>
     <t>Sunday spent at home with family</t>
-  </si>
-  <si>
-    <t>travelled from home and came directly to college selp less and rested after returning</t>
-  </si>
-  <si>
-    <t>long college day with many classes</t>
-  </si>
-  <si>
-    <t>attanded classes ad complete regular work</t>
-  </si>
-  <si>
-    <t>weekendrelexed and completed personal work</t>
-  </si>
-  <si>
-    <t>relexed Sunday and spent time on personal work</t>
-  </si>
-  <si>
-    <t>busy college day</t>
   </si>
   <si>
     <t>shorter college day</t>
@@ -946,7 +928,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N400"/>
+  <dimension ref="A1:N392"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.85546875" customWidth="1"/>
@@ -1102,11 +1084,9 @@
         <v>20</v>
       </c>
       <c r="I6" s="10">
-        <f t="shared" ref="I6:I68" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
         <v>780</v>
       </c>
       <c r="J6" s="10">
-        <f t="shared" ref="J6:J68" si="1">IF(I6="","",1440-I6)</f>
         <v>660</v>
       </c>
       <c r="K6" s="11" t="s">
@@ -1122,7 +1102,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="30">
+    <row r="7" spans="1:14">
       <c r="A7" s="8">
         <v>46253</v>
       </c>
@@ -1148,11 +1128,9 @@
         <v>20</v>
       </c>
       <c r="I7" s="10">
-        <f t="shared" si="0"/>
         <v>990</v>
       </c>
       <c r="J7" s="10">
-        <f t="shared" si="1"/>
         <v>450</v>
       </c>
       <c r="K7" s="11" t="s">
@@ -1194,11 +1172,9 @@
         <v>480</v>
       </c>
       <c r="I8" s="10">
-        <f t="shared" si="0"/>
         <v>940</v>
       </c>
       <c r="J8" s="10">
-        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="K8" s="11" t="s">
@@ -1214,7 +1190,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="30">
+    <row r="9" spans="1:14">
       <c r="A9" s="8">
         <v>46255</v>
       </c>
@@ -1240,11 +1216,9 @@
         <v>180</v>
       </c>
       <c r="I9" s="10">
-        <f t="shared" si="0"/>
         <v>980</v>
       </c>
       <c r="J9" s="10">
-        <f t="shared" si="1"/>
         <v>460</v>
       </c>
       <c r="K9" s="11" t="s">
@@ -1260,7 +1234,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="30">
+    <row r="10" spans="1:14">
       <c r="A10" s="8">
         <v>46256</v>
       </c>
@@ -1286,11 +1260,9 @@
         <v>500</v>
       </c>
       <c r="I10" s="10">
-        <f t="shared" si="0"/>
         <v>1030</v>
       </c>
       <c r="J10" s="10">
-        <f t="shared" si="1"/>
         <v>410</v>
       </c>
       <c r="K10" s="11" t="s">
@@ -1306,7 +1278,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="30">
+    <row r="11" spans="1:14">
       <c r="A11" s="8">
         <v>46257</v>
       </c>
@@ -1332,11 +1304,9 @@
         <v>180</v>
       </c>
       <c r="I11" s="10">
-        <f t="shared" si="0"/>
         <v>860</v>
       </c>
       <c r="J11" s="10">
-        <f t="shared" si="1"/>
         <v>580</v>
       </c>
       <c r="K11" s="11" t="s">
@@ -1352,7 +1322,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="30">
+    <row r="12" spans="1:14">
       <c r="A12" s="8">
         <v>46258</v>
       </c>
@@ -1378,11 +1348,9 @@
         <v>90</v>
       </c>
       <c r="I12" s="10">
-        <f t="shared" si="0"/>
         <v>1025</v>
       </c>
       <c r="J12" s="10">
-        <f t="shared" si="1"/>
         <v>415</v>
       </c>
       <c r="K12" s="11" t="s">
@@ -1398,7 +1366,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="30">
+    <row r="13" spans="1:14">
       <c r="A13" s="8">
         <v>46259</v>
       </c>
@@ -1424,11 +1392,9 @@
         <v>150</v>
       </c>
       <c r="I13" s="10">
-        <f t="shared" si="0"/>
         <v>800</v>
       </c>
       <c r="J13" s="10">
-        <f t="shared" si="1"/>
         <v>640</v>
       </c>
       <c r="K13" s="11" t="s">
@@ -1470,11 +1436,9 @@
         <v>150</v>
       </c>
       <c r="I14" s="10">
-        <f t="shared" si="0"/>
         <v>1040</v>
       </c>
       <c r="J14" s="10">
-        <f t="shared" si="1"/>
         <v>400</v>
       </c>
       <c r="K14" s="11" t="s">
@@ -1516,11 +1480,9 @@
         <v>80</v>
       </c>
       <c r="I15" s="10">
-        <f t="shared" si="0"/>
         <v>870</v>
       </c>
       <c r="J15" s="10">
-        <f t="shared" si="1"/>
         <v>570</v>
       </c>
       <c r="K15" s="11" t="s">
@@ -1536,7 +1498,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="30">
+    <row r="16" spans="1:14">
       <c r="A16" s="8">
         <v>46262</v>
       </c>
@@ -1562,11 +1524,9 @@
         <v>120</v>
       </c>
       <c r="I16" s="10">
-        <f t="shared" si="0"/>
         <v>940</v>
       </c>
       <c r="J16" s="10">
-        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="K16" s="11" t="s">
@@ -1608,11 +1568,9 @@
         <v>200</v>
       </c>
       <c r="I17" s="10">
-        <f t="shared" si="0"/>
         <v>870</v>
       </c>
       <c r="J17" s="10">
-        <f t="shared" si="1"/>
         <v>570</v>
       </c>
       <c r="K17" s="11" t="s">
@@ -1628,7 +1586,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="30">
+    <row r="18" spans="1:14">
       <c r="A18" s="8">
         <v>46264</v>
       </c>
@@ -1654,11 +1612,9 @@
         <v>300</v>
       </c>
       <c r="I18" s="10">
-        <f t="shared" si="0"/>
         <v>1000</v>
       </c>
       <c r="J18" s="10">
-        <f t="shared" si="1"/>
         <v>440</v>
       </c>
       <c r="K18" s="11" t="s">
@@ -1674,47 +1630,45 @@
         <v>73</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="60">
+    <row r="19" spans="1:14">
       <c r="A19" s="8">
-        <v>46265</v>
+        <v>46273</v>
       </c>
       <c r="B19" s="9">
-        <v>300</v>
+        <v>550</v>
       </c>
       <c r="C19" s="9">
+        <v>40</v>
+      </c>
+      <c r="D19" s="9">
         <v>120</v>
-      </c>
-      <c r="D19" s="9">
-        <v>20</v>
       </c>
       <c r="E19" s="9">
         <v>0</v>
       </c>
       <c r="F19" s="9">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G19" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H19" s="9">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="I19" s="10">
-        <f t="shared" si="0"/>
-        <v>760</v>
+        <v>970</v>
       </c>
       <c r="J19" s="10">
-        <f t="shared" si="1"/>
-        <v>680</v>
+        <v>470</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="L19" s="11" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M19" s="11" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="N19" s="12" t="s">
         <v>74</v>
@@ -1722,200 +1676,192 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="8">
-        <v>46266</v>
+        <v>46274</v>
       </c>
       <c r="B20" s="9">
-        <v>450</v>
+        <v>480</v>
       </c>
       <c r="C20" s="9">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="D20" s="9">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E20" s="9">
         <v>40</v>
       </c>
       <c r="F20" s="9">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="G20" s="9">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H20" s="9">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="I20" s="10">
-        <f t="shared" si="0"/>
-        <v>880</v>
+        <v>1140</v>
       </c>
       <c r="J20" s="10">
-        <f t="shared" si="1"/>
-        <v>560</v>
+        <v>300</v>
       </c>
       <c r="K20" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="L20" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="L20" s="11" t="s">
-        <v>50</v>
-      </c>
       <c r="M20" s="11" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="N20" s="12" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="30">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" s="8">
-        <v>46267</v>
+        <v>46275</v>
       </c>
       <c r="B21" s="9">
         <v>480</v>
       </c>
       <c r="C21" s="9">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D21" s="9">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="E21" s="9">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F21" s="9">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="G21" s="9">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H21" s="9">
-        <v>90</v>
+        <v>330</v>
       </c>
       <c r="I21" s="10">
-        <f t="shared" si="0"/>
-        <v>1220</v>
+        <v>1020</v>
       </c>
       <c r="J21" s="10">
-        <f t="shared" si="1"/>
-        <v>220</v>
+        <v>420</v>
       </c>
       <c r="K21" s="11" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="L21" s="11" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="M21" s="11" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="N21" s="12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="8">
-        <v>46268</v>
+        <v>46276</v>
       </c>
       <c r="B22" s="9">
-        <v>510</v>
+        <v>470</v>
       </c>
       <c r="C22" s="9">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="D22" s="9">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="E22" s="9">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F22" s="9">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="G22" s="9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H22" s="9">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="I22" s="10">
-        <f t="shared" si="0"/>
-        <v>1000</v>
+        <v>1120</v>
       </c>
       <c r="J22" s="10">
-        <f t="shared" si="1"/>
-        <v>440</v>
+        <v>320</v>
       </c>
       <c r="K22" s="11" t="s">
         <v>49</v>
       </c>
       <c r="L22" s="11" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M22" s="11" t="s">
         <v>51</v>
       </c>
       <c r="N22" s="12" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" ht="30">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" s="8">
-        <v>46269</v>
+        <v>46277</v>
       </c>
       <c r="B23" s="9">
-        <v>450</v>
+        <v>550</v>
       </c>
       <c r="C23" s="9">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D23" s="9">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E23" s="9">
         <v>80</v>
       </c>
       <c r="F23" s="9">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G23" s="9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H23" s="9">
-        <v>55</v>
+        <v>450</v>
       </c>
       <c r="I23" s="10">
-        <f t="shared" si="0"/>
-        <v>945</v>
+        <v>1160</v>
       </c>
       <c r="J23" s="10">
-        <f t="shared" si="1"/>
-        <v>495</v>
+        <v>280</v>
       </c>
       <c r="K23" s="11" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="L23" s="11" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="M23" s="11" t="s">
         <v>51</v>
       </c>
       <c r="N23" s="12" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" ht="30">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" s="8">
-        <v>46270</v>
+        <v>46278</v>
       </c>
       <c r="B24" s="9">
-        <v>720</v>
+        <v>660</v>
       </c>
       <c r="C24" s="9">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="D24" s="9">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="E24" s="9">
         <v>0</v>
@@ -1927,110 +1873,104 @@
         <v>0</v>
       </c>
       <c r="H24" s="9">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="I24" s="10">
-        <f t="shared" si="0"/>
-        <v>1250</v>
+        <v>1050</v>
       </c>
       <c r="J24" s="10">
-        <f t="shared" si="1"/>
-        <v>190</v>
+        <v>390</v>
       </c>
       <c r="K24" s="11" t="s">
         <v>49</v>
       </c>
       <c r="L24" s="11" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M24" s="11" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="N24" s="12" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" ht="30">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" s="8">
-        <v>46271</v>
+        <v>46279</v>
       </c>
       <c r="B25" s="9">
-        <v>690</v>
+        <v>500</v>
       </c>
       <c r="C25" s="9">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="D25" s="9">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E25" s="9">
         <v>0</v>
       </c>
       <c r="F25" s="9">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G25" s="9">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H25" s="9">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="I25" s="10">
-        <f t="shared" si="0"/>
-        <v>1090</v>
+        <v>980</v>
       </c>
       <c r="J25" s="10">
-        <f t="shared" si="1"/>
-        <v>350</v>
+        <v>460</v>
       </c>
       <c r="K25" s="11" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="L25" s="11" t="s">
         <v>56</v>
       </c>
       <c r="M25" s="11" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="N25" s="12" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="8">
-        <v>46272</v>
+        <v>46280</v>
       </c>
       <c r="B26" s="9">
-        <v>480</v>
+        <v>450</v>
       </c>
       <c r="C26" s="9">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D26" s="9">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="E26" s="9">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F26" s="9">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="G26" s="9">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H26" s="9">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="I26" s="10">
-        <f t="shared" si="0"/>
-        <v>1125</v>
+        <v>860</v>
       </c>
       <c r="J26" s="10">
-        <f t="shared" si="1"/>
-        <v>315</v>
+        <v>580</v>
       </c>
       <c r="K26" s="11" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="L26" s="11" t="s">
         <v>50</v>
@@ -2039,208 +1979,200 @@
         <v>51</v>
       </c>
       <c r="N26" s="12" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="8">
-        <v>46273</v>
+        <v>46281</v>
       </c>
       <c r="B27" s="9">
-        <v>550</v>
+        <v>479</v>
       </c>
       <c r="C27" s="9">
+        <v>80</v>
+      </c>
+      <c r="D27" s="9">
+        <v>60</v>
+      </c>
+      <c r="E27" s="9">
         <v>40</v>
       </c>
-      <c r="D27" s="9">
+      <c r="F27" s="9">
+        <v>400</v>
+      </c>
+      <c r="G27" s="9">
+        <v>8</v>
+      </c>
+      <c r="H27" s="9">
+        <v>90</v>
+      </c>
+      <c r="I27" s="10">
+        <v>1149</v>
+      </c>
+      <c r="J27" s="10">
+        <v>291</v>
+      </c>
+      <c r="K27" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="L27" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M27" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="N27" s="12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" s="8">
+        <v>46282</v>
+      </c>
+      <c r="B28" s="9">
+        <v>500</v>
+      </c>
+      <c r="C28" s="9">
+        <v>100</v>
+      </c>
+      <c r="D28" s="9">
+        <v>60</v>
+      </c>
+      <c r="E28" s="9">
+        <v>0</v>
+      </c>
+      <c r="F28" s="9">
+        <v>250</v>
+      </c>
+      <c r="G28" s="9">
+        <v>5</v>
+      </c>
+      <c r="H28" s="9">
         <v>120</v>
       </c>
-      <c r="E27" s="9">
-        <v>0</v>
-      </c>
-      <c r="F27" s="9">
+      <c r="I28" s="10">
+        <v>1030</v>
+      </c>
+      <c r="J28" s="10">
+        <v>410</v>
+      </c>
+      <c r="K28" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L28" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M28" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N28" s="12" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" s="8">
+        <v>46283</v>
+      </c>
+      <c r="B29" s="9">
+        <v>450</v>
+      </c>
+      <c r="C29" s="9">
+        <v>80</v>
+      </c>
+      <c r="D29" s="9">
+        <v>120</v>
+      </c>
+      <c r="E29" s="9">
+        <v>50</v>
+      </c>
+      <c r="F29" s="9">
+        <v>250</v>
+      </c>
+      <c r="G29" s="9">
+        <v>5</v>
+      </c>
+      <c r="H29" s="9">
         <v>100</v>
       </c>
-      <c r="G27" s="9">
-        <v>2</v>
-      </c>
-      <c r="H27" s="9">
-        <v>160</v>
-      </c>
-      <c r="I27" s="10">
-        <f t="shared" si="0"/>
-        <v>970</v>
-      </c>
-      <c r="J27" s="10">
-        <f t="shared" si="1"/>
-        <v>470</v>
-      </c>
-      <c r="K27" s="11" t="s">
+      <c r="I29" s="10">
+        <v>1050</v>
+      </c>
+      <c r="J29" s="10">
+        <v>390</v>
+      </c>
+      <c r="K29" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="L27" s="11" t="s">
+      <c r="L29" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="M27" s="11" t="s">
+      <c r="M29" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="N27" s="12" t="s">
+      <c r="N29" s="12" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" s="8">
+        <v>46284</v>
+      </c>
+      <c r="B30" s="9">
+        <v>500</v>
+      </c>
+      <c r="C30" s="9">
         <v>80</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" ht="30">
-      <c r="A28" s="8">
-        <v>46274</v>
-      </c>
-      <c r="B28" s="9">
-        <v>480</v>
-      </c>
-      <c r="C28" s="9">
-        <v>80</v>
-      </c>
-      <c r="D28" s="9">
-        <v>50</v>
-      </c>
-      <c r="E28" s="9">
-        <v>40</v>
-      </c>
-      <c r="F28" s="9">
-        <v>400</v>
-      </c>
-      <c r="G28" s="9">
-        <v>8</v>
-      </c>
-      <c r="H28" s="9">
-        <v>90</v>
-      </c>
-      <c r="I28" s="10">
-        <f t="shared" si="0"/>
-        <v>1140</v>
-      </c>
-      <c r="J28" s="10">
-        <f t="shared" si="1"/>
-        <v>300</v>
-      </c>
-      <c r="K28" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="L28" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="M28" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="N28" s="12" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" ht="30">
-      <c r="A29" s="8">
-        <v>46275</v>
-      </c>
-      <c r="B29" s="9">
-        <v>480</v>
-      </c>
-      <c r="C29" s="9">
-        <v>60</v>
-      </c>
-      <c r="D29" s="9">
-        <v>0</v>
-      </c>
-      <c r="E29" s="9">
-        <v>0</v>
-      </c>
-      <c r="F29" s="9">
-        <v>150</v>
-      </c>
-      <c r="G29" s="9">
-        <v>3</v>
-      </c>
-      <c r="H29" s="9">
-        <v>330</v>
-      </c>
-      <c r="I29" s="10">
-        <f t="shared" si="0"/>
-        <v>1020</v>
-      </c>
-      <c r="J29" s="10">
-        <f t="shared" si="1"/>
-        <v>420</v>
-      </c>
-      <c r="K29" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="L29" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="M29" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="N29" s="12" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" ht="30">
-      <c r="A30" s="8">
-        <v>46276</v>
-      </c>
-      <c r="B30" s="9">
-        <v>470</v>
-      </c>
-      <c r="C30" s="9">
-        <v>100</v>
       </c>
       <c r="D30" s="9">
         <v>0</v>
       </c>
       <c r="E30" s="9">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F30" s="9">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="G30" s="9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H30" s="9">
-        <v>350</v>
+        <v>120</v>
       </c>
       <c r="I30" s="10">
-        <f t="shared" si="0"/>
-        <v>1120</v>
+        <v>700</v>
       </c>
       <c r="J30" s="10">
-        <f t="shared" si="1"/>
-        <v>320</v>
+        <v>740</v>
       </c>
       <c r="K30" s="11" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="L30" s="11" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="M30" s="11" t="s">
         <v>51</v>
       </c>
       <c r="N30" s="12" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="8">
-        <v>46277</v>
+        <v>46285</v>
       </c>
       <c r="B31" s="9">
-        <v>550</v>
+        <v>600</v>
       </c>
       <c r="C31" s="9">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="D31" s="9">
+        <v>220</v>
+      </c>
+      <c r="E31" s="9">
         <v>0</v>
-      </c>
-      <c r="E31" s="9">
-        <v>80</v>
       </c>
       <c r="F31" s="9">
         <v>0</v>
@@ -2249,64 +2181,60 @@
         <v>0</v>
       </c>
       <c r="H31" s="9">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="I31" s="10">
-        <f t="shared" si="0"/>
-        <v>1160</v>
+        <v>1180</v>
       </c>
       <c r="J31" s="10">
-        <f t="shared" si="1"/>
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="K31" s="11" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="L31" s="11" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M31" s="11" t="s">
         <v>51</v>
       </c>
       <c r="N31" s="12" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" ht="30">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
       <c r="A32" s="8">
-        <v>46278</v>
+        <v>46286</v>
       </c>
       <c r="B32" s="9">
-        <v>660</v>
+        <v>500</v>
       </c>
       <c r="C32" s="9">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="D32" s="9">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="E32" s="9">
         <v>0</v>
       </c>
       <c r="F32" s="9">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G32" s="9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H32" s="9">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I32" s="10">
-        <f t="shared" si="0"/>
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="J32" s="10">
-        <f t="shared" si="1"/>
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="K32" s="11" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="L32" s="11" t="s">
         <v>50</v>
@@ -2315,376 +2243,184 @@
         <v>51</v>
       </c>
       <c r="N32" s="12" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" ht="30">
-      <c r="A33" s="8">
-        <v>46279</v>
-      </c>
-      <c r="B33" s="9">
-        <v>500</v>
-      </c>
-      <c r="C33" s="9">
-        <v>60</v>
-      </c>
-      <c r="D33" s="9">
-        <v>0</v>
-      </c>
-      <c r="E33" s="9">
-        <v>0</v>
-      </c>
-      <c r="F33" s="9">
-        <v>300</v>
-      </c>
-      <c r="G33" s="9">
-        <v>6</v>
-      </c>
-      <c r="H33" s="9">
-        <v>120</v>
-      </c>
-      <c r="I33" s="10">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
+      <c r="A33" s="8"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
+      <c r="I33" s="10" t="str">
+        <f t="shared" ref="I33:I60" si="0">IF(SUM(B33:F33,H33)=0,"",SUM(B33:F33,H33))</f>
+        <v/>
+      </c>
+      <c r="J33" s="10" t="str">
+        <f t="shared" ref="J33:J60" si="1">IF(I33="","",1440-I33)</f>
+        <v/>
+      </c>
+      <c r="K33" s="11"/>
+      <c r="L33" s="11"/>
+      <c r="M33" s="11"/>
+      <c r="N33" s="12"/>
+    </row>
+    <row r="34" spans="1:14">
+      <c r="A34" s="8"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="9"/>
+      <c r="I34" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>980</v>
-      </c>
-      <c r="J33" s="10">
+        <v/>
+      </c>
+      <c r="J34" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>460</v>
-      </c>
-      <c r="K33" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="L33" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="M33" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="N33" s="12" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" ht="30">
-      <c r="A34" s="8">
-        <v>46280</v>
-      </c>
-      <c r="B34" s="9">
-        <v>450</v>
-      </c>
-      <c r="C34" s="9">
-        <v>80</v>
-      </c>
-      <c r="D34" s="9">
-        <v>60</v>
-      </c>
-      <c r="E34" s="9">
-        <v>0</v>
-      </c>
-      <c r="F34" s="9">
-        <v>150</v>
-      </c>
-      <c r="G34" s="9">
-        <v>3</v>
-      </c>
-      <c r="H34" s="9">
-        <v>120</v>
-      </c>
-      <c r="I34" s="10">
+        <v/>
+      </c>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+      <c r="M34" s="11"/>
+      <c r="N34" s="12"/>
+    </row>
+    <row r="35" spans="1:14">
+      <c r="A35" s="8"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="9"/>
+      <c r="I35" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>860</v>
-      </c>
-      <c r="J34" s="10">
+        <v/>
+      </c>
+      <c r="J35" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>580</v>
-      </c>
-      <c r="K34" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="L34" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M34" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N34" s="12" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" ht="30">
-      <c r="A35" s="8">
-        <v>46281</v>
-      </c>
-      <c r="B35" s="9">
-        <v>479</v>
-      </c>
-      <c r="C35" s="9">
-        <v>80</v>
-      </c>
-      <c r="D35" s="9">
-        <v>60</v>
-      </c>
-      <c r="E35" s="9">
-        <v>40</v>
-      </c>
-      <c r="F35" s="9">
-        <v>400</v>
-      </c>
-      <c r="G35" s="9">
-        <v>8</v>
-      </c>
-      <c r="H35" s="9">
-        <v>90</v>
-      </c>
-      <c r="I35" s="10">
+        <v/>
+      </c>
+      <c r="K35" s="11"/>
+      <c r="L35" s="11"/>
+      <c r="M35" s="11"/>
+      <c r="N35" s="12"/>
+    </row>
+    <row r="36" spans="1:14">
+      <c r="A36" s="8"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="9"/>
+      <c r="I36" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>1149</v>
-      </c>
-      <c r="J35" s="10">
+        <v/>
+      </c>
+      <c r="J36" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>291</v>
-      </c>
-      <c r="K35" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="L35" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="M35" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="N35" s="12" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14">
-      <c r="A36" s="8">
-        <v>46282</v>
-      </c>
-      <c r="B36" s="9">
-        <v>500</v>
-      </c>
-      <c r="C36" s="9">
-        <v>100</v>
-      </c>
-      <c r="D36" s="9">
-        <v>60</v>
-      </c>
-      <c r="E36" s="9">
-        <v>0</v>
-      </c>
-      <c r="F36" s="9">
-        <v>250</v>
-      </c>
-      <c r="G36" s="9">
-        <v>5</v>
-      </c>
-      <c r="H36" s="9">
-        <v>120</v>
-      </c>
-      <c r="I36" s="10">
+        <v/>
+      </c>
+      <c r="K36" s="11"/>
+      <c r="L36" s="11"/>
+      <c r="M36" s="11"/>
+      <c r="N36" s="12"/>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37" s="8"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
+      <c r="I37" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>1030</v>
-      </c>
-      <c r="J36" s="10">
+        <v/>
+      </c>
+      <c r="J37" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>410</v>
-      </c>
-      <c r="K36" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="L36" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M36" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N36" s="12" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" ht="30">
-      <c r="A37" s="8">
-        <v>46283</v>
-      </c>
-      <c r="B37" s="9">
-        <v>450</v>
-      </c>
-      <c r="C37" s="9">
-        <v>80</v>
-      </c>
-      <c r="D37" s="9">
-        <v>120</v>
-      </c>
-      <c r="E37" s="9">
-        <v>50</v>
-      </c>
-      <c r="F37" s="9">
-        <v>250</v>
-      </c>
-      <c r="G37" s="9">
-        <v>5</v>
-      </c>
-      <c r="H37" s="9">
-        <v>100</v>
-      </c>
-      <c r="I37" s="10">
+        <v/>
+      </c>
+      <c r="K37" s="11"/>
+      <c r="L37" s="11"/>
+      <c r="M37" s="11"/>
+      <c r="N37" s="12"/>
+    </row>
+    <row r="38" spans="1:14">
+      <c r="A38" s="8"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="9"/>
+      <c r="I38" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>1050</v>
-      </c>
-      <c r="J37" s="10">
+        <v/>
+      </c>
+      <c r="J38" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>390</v>
-      </c>
-      <c r="K37" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="L37" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M37" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N37" s="12" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" ht="30">
-      <c r="A38" s="8">
-        <v>46284</v>
-      </c>
-      <c r="B38" s="9">
-        <v>500</v>
-      </c>
-      <c r="C38" s="9">
-        <v>80</v>
-      </c>
-      <c r="D38" s="9">
-        <v>0</v>
-      </c>
-      <c r="E38" s="9">
-        <v>0</v>
-      </c>
-      <c r="F38" s="9">
-        <v>0</v>
-      </c>
-      <c r="G38" s="9">
-        <v>0</v>
-      </c>
-      <c r="H38" s="9">
-        <v>120</v>
-      </c>
-      <c r="I38" s="10">
+        <v/>
+      </c>
+      <c r="K38" s="11"/>
+      <c r="L38" s="11"/>
+      <c r="M38" s="11"/>
+      <c r="N38" s="12"/>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="A39" s="8"/>
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="9"/>
+      <c r="H39" s="9"/>
+      <c r="I39" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>700</v>
-      </c>
-      <c r="J38" s="10">
+        <v/>
+      </c>
+      <c r="J39" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>740</v>
-      </c>
-      <c r="K38" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="L38" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="M38" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N38" s="12" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" ht="30">
-      <c r="A39" s="8">
-        <v>46285</v>
-      </c>
-      <c r="B39" s="9">
-        <v>600</v>
-      </c>
-      <c r="C39" s="9">
-        <v>60</v>
-      </c>
-      <c r="D39" s="9">
-        <v>220</v>
-      </c>
-      <c r="E39" s="9">
-        <v>0</v>
-      </c>
-      <c r="F39" s="9">
-        <v>0</v>
-      </c>
-      <c r="G39" s="9">
-        <v>0</v>
-      </c>
-      <c r="H39" s="9">
-        <v>300</v>
-      </c>
-      <c r="I39" s="10">
+        <v/>
+      </c>
+      <c r="K39" s="11"/>
+      <c r="L39" s="11"/>
+      <c r="M39" s="11"/>
+      <c r="N39" s="12"/>
+    </row>
+    <row r="40" spans="1:14">
+      <c r="A40" s="8"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="9"/>
+      <c r="I40" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>1180</v>
-      </c>
-      <c r="J39" s="10">
+        <v/>
+      </c>
+      <c r="J40" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>260</v>
-      </c>
-      <c r="K39" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="L39" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M39" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N39" s="12" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" ht="45">
-      <c r="A40" s="8">
-        <v>46286</v>
-      </c>
-      <c r="B40" s="9">
-        <v>500</v>
-      </c>
-      <c r="C40" s="9">
-        <v>60</v>
-      </c>
-      <c r="D40" s="9">
-        <v>150</v>
-      </c>
-      <c r="E40" s="9">
-        <v>0</v>
-      </c>
-      <c r="F40" s="9">
-        <v>300</v>
-      </c>
-      <c r="G40" s="9">
-        <v>5</v>
-      </c>
-      <c r="H40" s="9">
-        <v>30</v>
-      </c>
-      <c r="I40" s="10">
-        <f t="shared" si="0"/>
-        <v>1040</v>
-      </c>
-      <c r="J40" s="10">
-        <f t="shared" si="1"/>
-        <v>400</v>
-      </c>
-      <c r="K40" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="L40" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M40" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N40" s="12" t="s">
-        <v>95</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K40" s="11"/>
+      <c r="L40" s="11"/>
+      <c r="M40" s="11"/>
+      <c r="N40" s="12"/>
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="8"/>
@@ -3136,11 +2872,11 @@
       <c r="G61" s="9"/>
       <c r="H61" s="9"/>
       <c r="I61" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I61:I124" si="2">IF(SUM(B61:F61,H61)=0,"",SUM(B61:F61,H61))</f>
         <v/>
       </c>
       <c r="J61" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J61:J124" si="3">IF(I61="","",1440-I61)</f>
         <v/>
       </c>
       <c r="K61" s="11"/>
@@ -3158,11 +2894,11 @@
       <c r="G62" s="9"/>
       <c r="H62" s="9"/>
       <c r="I62" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J62" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K62" s="11"/>
@@ -3180,11 +2916,11 @@
       <c r="G63" s="9"/>
       <c r="H63" s="9"/>
       <c r="I63" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J63" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K63" s="11"/>
@@ -3202,11 +2938,11 @@
       <c r="G64" s="9"/>
       <c r="H64" s="9"/>
       <c r="I64" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J64" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K64" s="11"/>
@@ -3224,11 +2960,11 @@
       <c r="G65" s="9"/>
       <c r="H65" s="9"/>
       <c r="I65" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J65" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K65" s="11"/>
@@ -3246,11 +2982,11 @@
       <c r="G66" s="9"/>
       <c r="H66" s="9"/>
       <c r="I66" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J66" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K66" s="11"/>
@@ -3268,11 +3004,11 @@
       <c r="G67" s="9"/>
       <c r="H67" s="9"/>
       <c r="I67" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J67" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K67" s="11"/>
@@ -3290,11 +3026,11 @@
       <c r="G68" s="9"/>
       <c r="H68" s="9"/>
       <c r="I68" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J68" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K68" s="11"/>
@@ -3312,11 +3048,11 @@
       <c r="G69" s="9"/>
       <c r="H69" s="9"/>
       <c r="I69" s="10" t="str">
-        <f t="shared" ref="I69:I132" si="2">IF(SUM(B69:F69,H69)=0,"",SUM(B69:F69,H69))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J69" s="10" t="str">
-        <f t="shared" ref="J69:J132" si="3">IF(I69="","",1440-I69)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K69" s="11"/>
@@ -4544,11 +4280,11 @@
       <c r="G125" s="9"/>
       <c r="H125" s="9"/>
       <c r="I125" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="I125:I188" si="4">IF(SUM(B125:F125,H125)=0,"",SUM(B125:F125,H125))</f>
         <v/>
       </c>
       <c r="J125" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="J125:J188" si="5">IF(I125="","",1440-I125)</f>
         <v/>
       </c>
       <c r="K125" s="11"/>
@@ -4566,11 +4302,11 @@
       <c r="G126" s="9"/>
       <c r="H126" s="9"/>
       <c r="I126" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J126" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K126" s="11"/>
@@ -4588,11 +4324,11 @@
       <c r="G127" s="9"/>
       <c r="H127" s="9"/>
       <c r="I127" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J127" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K127" s="11"/>
@@ -4610,11 +4346,11 @@
       <c r="G128" s="9"/>
       <c r="H128" s="9"/>
       <c r="I128" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J128" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K128" s="11"/>
@@ -4632,11 +4368,11 @@
       <c r="G129" s="9"/>
       <c r="H129" s="9"/>
       <c r="I129" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J129" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K129" s="11"/>
@@ -4654,11 +4390,11 @@
       <c r="G130" s="9"/>
       <c r="H130" s="9"/>
       <c r="I130" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J130" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K130" s="11"/>
@@ -4676,11 +4412,11 @@
       <c r="G131" s="9"/>
       <c r="H131" s="9"/>
       <c r="I131" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J131" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K131" s="11"/>
@@ -4698,11 +4434,11 @@
       <c r="G132" s="9"/>
       <c r="H132" s="9"/>
       <c r="I132" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J132" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K132" s="11"/>
@@ -4720,11 +4456,11 @@
       <c r="G133" s="9"/>
       <c r="H133" s="9"/>
       <c r="I133" s="10" t="str">
-        <f t="shared" ref="I133:I196" si="4">IF(SUM(B133:F133,H133)=0,"",SUM(B133:F133,H133))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J133" s="10" t="str">
-        <f t="shared" ref="J133:J196" si="5">IF(I133="","",1440-I133)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K133" s="11"/>
@@ -5952,11 +5688,11 @@
       <c r="G189" s="9"/>
       <c r="H189" s="9"/>
       <c r="I189" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="I189:I252" si="6">IF(SUM(B189:F189,H189)=0,"",SUM(B189:F189,H189))</f>
         <v/>
       </c>
       <c r="J189" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J189:J252" si="7">IF(I189="","",1440-I189)</f>
         <v/>
       </c>
       <c r="K189" s="11"/>
@@ -5974,11 +5710,11 @@
       <c r="G190" s="9"/>
       <c r="H190" s="9"/>
       <c r="I190" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J190" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K190" s="11"/>
@@ -5996,11 +5732,11 @@
       <c r="G191" s="9"/>
       <c r="H191" s="9"/>
       <c r="I191" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J191" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K191" s="11"/>
@@ -6018,11 +5754,11 @@
       <c r="G192" s="9"/>
       <c r="H192" s="9"/>
       <c r="I192" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J192" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K192" s="11"/>
@@ -6040,11 +5776,11 @@
       <c r="G193" s="9"/>
       <c r="H193" s="9"/>
       <c r="I193" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J193" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K193" s="11"/>
@@ -6062,11 +5798,11 @@
       <c r="G194" s="9"/>
       <c r="H194" s="9"/>
       <c r="I194" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J194" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K194" s="11"/>
@@ -6084,11 +5820,11 @@
       <c r="G195" s="9"/>
       <c r="H195" s="9"/>
       <c r="I195" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J195" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K195" s="11"/>
@@ -6106,11 +5842,11 @@
       <c r="G196" s="9"/>
       <c r="H196" s="9"/>
       <c r="I196" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J196" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K196" s="11"/>
@@ -6128,11 +5864,11 @@
       <c r="G197" s="9"/>
       <c r="H197" s="9"/>
       <c r="I197" s="10" t="str">
-        <f t="shared" ref="I197:I260" si="6">IF(SUM(B197:F197,H197)=0,"",SUM(B197:F197,H197))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J197" s="10" t="str">
-        <f t="shared" ref="J197:J260" si="7">IF(I197="","",1440-I197)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K197" s="11"/>
@@ -7360,11 +7096,11 @@
       <c r="G253" s="9"/>
       <c r="H253" s="9"/>
       <c r="I253" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I253:I316" si="8">IF(SUM(B253:F253,H253)=0,"",SUM(B253:F253,H253))</f>
         <v/>
       </c>
       <c r="J253" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J253:J316" si="9">IF(I253="","",1440-I253)</f>
         <v/>
       </c>
       <c r="K253" s="11"/>
@@ -7382,11 +7118,11 @@
       <c r="G254" s="9"/>
       <c r="H254" s="9"/>
       <c r="I254" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J254" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K254" s="11"/>
@@ -7404,11 +7140,11 @@
       <c r="G255" s="9"/>
       <c r="H255" s="9"/>
       <c r="I255" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J255" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K255" s="11"/>
@@ -7426,11 +7162,11 @@
       <c r="G256" s="9"/>
       <c r="H256" s="9"/>
       <c r="I256" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J256" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K256" s="11"/>
@@ -7448,11 +7184,11 @@
       <c r="G257" s="9"/>
       <c r="H257" s="9"/>
       <c r="I257" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J257" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K257" s="11"/>
@@ -7470,11 +7206,11 @@
       <c r="G258" s="9"/>
       <c r="H258" s="9"/>
       <c r="I258" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J258" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K258" s="11"/>
@@ -7492,11 +7228,11 @@
       <c r="G259" s="9"/>
       <c r="H259" s="9"/>
       <c r="I259" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J259" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K259" s="11"/>
@@ -7514,11 +7250,11 @@
       <c r="G260" s="9"/>
       <c r="H260" s="9"/>
       <c r="I260" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J260" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K260" s="11"/>
@@ -7536,11 +7272,11 @@
       <c r="G261" s="9"/>
       <c r="H261" s="9"/>
       <c r="I261" s="10" t="str">
-        <f t="shared" ref="I261:I324" si="8">IF(SUM(B261:F261,H261)=0,"",SUM(B261:F261,H261))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J261" s="10" t="str">
-        <f t="shared" ref="J261:J324" si="9">IF(I261="","",1440-I261)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K261" s="11"/>
@@ -8768,11 +8504,11 @@
       <c r="G317" s="9"/>
       <c r="H317" s="9"/>
       <c r="I317" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I317:I380" si="10">IF(SUM(B317:F317,H317)=0,"",SUM(B317:F317,H317))</f>
         <v/>
       </c>
       <c r="J317" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J317:J380" si="11">IF(I317="","",1440-I317)</f>
         <v/>
       </c>
       <c r="K317" s="11"/>
@@ -8790,11 +8526,11 @@
       <c r="G318" s="9"/>
       <c r="H318" s="9"/>
       <c r="I318" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J318" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K318" s="11"/>
@@ -8812,11 +8548,11 @@
       <c r="G319" s="9"/>
       <c r="H319" s="9"/>
       <c r="I319" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J319" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K319" s="11"/>
@@ -8834,11 +8570,11 @@
       <c r="G320" s="9"/>
       <c r="H320" s="9"/>
       <c r="I320" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J320" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K320" s="11"/>
@@ -8856,11 +8592,11 @@
       <c r="G321" s="9"/>
       <c r="H321" s="9"/>
       <c r="I321" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J321" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K321" s="11"/>
@@ -8878,11 +8614,11 @@
       <c r="G322" s="9"/>
       <c r="H322" s="9"/>
       <c r="I322" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J322" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K322" s="11"/>
@@ -8900,11 +8636,11 @@
       <c r="G323" s="9"/>
       <c r="H323" s="9"/>
       <c r="I323" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J323" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K323" s="11"/>
@@ -8922,11 +8658,11 @@
       <c r="G324" s="9"/>
       <c r="H324" s="9"/>
       <c r="I324" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J324" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K324" s="11"/>
@@ -8944,11 +8680,11 @@
       <c r="G325" s="9"/>
       <c r="H325" s="9"/>
       <c r="I325" s="10" t="str">
-        <f t="shared" ref="I325:I388" si="10">IF(SUM(B325:F325,H325)=0,"",SUM(B325:F325,H325))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J325" s="10" t="str">
-        <f t="shared" ref="J325:J388" si="11">IF(I325="","",1440-I325)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K325" s="11"/>
@@ -10176,11 +9912,11 @@
       <c r="G381" s="9"/>
       <c r="H381" s="9"/>
       <c r="I381" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I381:I392" si="12">IF(SUM(B381:F381,H381)=0,"",SUM(B381:F381,H381))</f>
         <v/>
       </c>
       <c r="J381" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J381:J392" si="13">IF(I381="","",1440-I381)</f>
         <v/>
       </c>
       <c r="K381" s="11"/>
@@ -10198,11 +9934,11 @@
       <c r="G382" s="9"/>
       <c r="H382" s="9"/>
       <c r="I382" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J382" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K382" s="11"/>
@@ -10220,11 +9956,11 @@
       <c r="G383" s="9"/>
       <c r="H383" s="9"/>
       <c r="I383" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J383" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K383" s="11"/>
@@ -10242,11 +9978,11 @@
       <c r="G384" s="9"/>
       <c r="H384" s="9"/>
       <c r="I384" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J384" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K384" s="11"/>
@@ -10264,11 +10000,11 @@
       <c r="G385" s="9"/>
       <c r="H385" s="9"/>
       <c r="I385" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J385" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K385" s="11"/>
@@ -10286,11 +10022,11 @@
       <c r="G386" s="9"/>
       <c r="H386" s="9"/>
       <c r="I386" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J386" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K386" s="11"/>
@@ -10308,11 +10044,11 @@
       <c r="G387" s="9"/>
       <c r="H387" s="9"/>
       <c r="I387" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J387" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K387" s="11"/>
@@ -10330,11 +10066,11 @@
       <c r="G388" s="9"/>
       <c r="H388" s="9"/>
       <c r="I388" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J388" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K388" s="11"/>
@@ -10352,11 +10088,11 @@
       <c r="G389" s="9"/>
       <c r="H389" s="9"/>
       <c r="I389" s="10" t="str">
-        <f t="shared" ref="I389:I400" si="12">IF(SUM(B389:F389,H389)=0,"",SUM(B389:F389,H389))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J389" s="10" t="str">
-        <f t="shared" ref="J389:J400" si="13">IF(I389="","",1440-I389)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K389" s="11"/>
@@ -10430,182 +10166,6 @@
       <c r="M392" s="11"/>
       <c r="N392" s="12"/>
     </row>
-    <row r="393" spans="1:14">
-      <c r="A393" s="8"/>
-      <c r="B393" s="9"/>
-      <c r="C393" s="9"/>
-      <c r="D393" s="9"/>
-      <c r="E393" s="9"/>
-      <c r="F393" s="9"/>
-      <c r="G393" s="9"/>
-      <c r="H393" s="9"/>
-      <c r="I393" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J393" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K393" s="11"/>
-      <c r="L393" s="11"/>
-      <c r="M393" s="11"/>
-      <c r="N393" s="12"/>
-    </row>
-    <row r="394" spans="1:14">
-      <c r="A394" s="8"/>
-      <c r="B394" s="9"/>
-      <c r="C394" s="9"/>
-      <c r="D394" s="9"/>
-      <c r="E394" s="9"/>
-      <c r="F394" s="9"/>
-      <c r="G394" s="9"/>
-      <c r="H394" s="9"/>
-      <c r="I394" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J394" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K394" s="11"/>
-      <c r="L394" s="11"/>
-      <c r="M394" s="11"/>
-      <c r="N394" s="12"/>
-    </row>
-    <row r="395" spans="1:14">
-      <c r="A395" s="8"/>
-      <c r="B395" s="9"/>
-      <c r="C395" s="9"/>
-      <c r="D395" s="9"/>
-      <c r="E395" s="9"/>
-      <c r="F395" s="9"/>
-      <c r="G395" s="9"/>
-      <c r="H395" s="9"/>
-      <c r="I395" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J395" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K395" s="11"/>
-      <c r="L395" s="11"/>
-      <c r="M395" s="11"/>
-      <c r="N395" s="12"/>
-    </row>
-    <row r="396" spans="1:14">
-      <c r="A396" s="8"/>
-      <c r="B396" s="9"/>
-      <c r="C396" s="9"/>
-      <c r="D396" s="9"/>
-      <c r="E396" s="9"/>
-      <c r="F396" s="9"/>
-      <c r="G396" s="9"/>
-      <c r="H396" s="9"/>
-      <c r="I396" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J396" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K396" s="11"/>
-      <c r="L396" s="11"/>
-      <c r="M396" s="11"/>
-      <c r="N396" s="12"/>
-    </row>
-    <row r="397" spans="1:14">
-      <c r="A397" s="8"/>
-      <c r="B397" s="9"/>
-      <c r="C397" s="9"/>
-      <c r="D397" s="9"/>
-      <c r="E397" s="9"/>
-      <c r="F397" s="9"/>
-      <c r="G397" s="9"/>
-      <c r="H397" s="9"/>
-      <c r="I397" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J397" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K397" s="11"/>
-      <c r="L397" s="11"/>
-      <c r="M397" s="11"/>
-      <c r="N397" s="12"/>
-    </row>
-    <row r="398" spans="1:14">
-      <c r="A398" s="8"/>
-      <c r="B398" s="9"/>
-      <c r="C398" s="9"/>
-      <c r="D398" s="9"/>
-      <c r="E398" s="9"/>
-      <c r="F398" s="9"/>
-      <c r="G398" s="9"/>
-      <c r="H398" s="9"/>
-      <c r="I398" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J398" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K398" s="11"/>
-      <c r="L398" s="11"/>
-      <c r="M398" s="11"/>
-      <c r="N398" s="12"/>
-    </row>
-    <row r="399" spans="1:14">
-      <c r="A399" s="8"/>
-      <c r="B399" s="9"/>
-      <c r="C399" s="9"/>
-      <c r="D399" s="9"/>
-      <c r="E399" s="9"/>
-      <c r="F399" s="9"/>
-      <c r="G399" s="9"/>
-      <c r="H399" s="9"/>
-      <c r="I399" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J399" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K399" s="11"/>
-      <c r="L399" s="11"/>
-      <c r="M399" s="11"/>
-      <c r="N399" s="12"/>
-    </row>
-    <row r="400" spans="1:14">
-      <c r="A400" s="8"/>
-      <c r="B400" s="9"/>
-      <c r="C400" s="9"/>
-      <c r="D400" s="9"/>
-      <c r="E400" s="9"/>
-      <c r="F400" s="9"/>
-      <c r="G400" s="9"/>
-      <c r="H400" s="9"/>
-      <c r="I400" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J400" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K400" s="11"/>
-      <c r="L400" s="11"/>
-      <c r="M400" s="11"/>
-      <c r="N400" s="12"/>
-    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A4:N4"/>
@@ -10615,21 +10175,21 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J400">
+  <conditionalFormatting sqref="J6:J392">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K400">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K392">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L400">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L392">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M400">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M392">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/12602999.xlsx
+++ b/12602999.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="92">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -301,6 +301,12 @@
   </si>
   <si>
     <t xml:space="preserve"> attended regular classes and participated in an active listening workshop </t>
+  </si>
+  <si>
+    <t>attanded 2 makeup classes</t>
+  </si>
+  <si>
+    <t>tired after attendeing classes</t>
   </si>
 </sst>
 </file>
@@ -1102,7 +1108,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" ht="30">
       <c r="A7" s="8">
         <v>46253</v>
       </c>
@@ -1190,7 +1196,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" ht="30">
       <c r="A9" s="8">
         <v>46255</v>
       </c>
@@ -1234,7 +1240,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" ht="30">
       <c r="A10" s="8">
         <v>46256</v>
       </c>
@@ -1278,7 +1284,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" ht="30">
       <c r="A11" s="8">
         <v>46257</v>
       </c>
@@ -1322,7 +1328,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" ht="30">
       <c r="A12" s="8">
         <v>46258</v>
       </c>
@@ -1366,7 +1372,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" ht="30">
       <c r="A13" s="8">
         <v>46259</v>
       </c>
@@ -1498,7 +1504,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:14" ht="30">
       <c r="A16" s="8">
         <v>46262</v>
       </c>
@@ -1586,7 +1592,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:14" ht="30">
       <c r="A18" s="8">
         <v>46264</v>
       </c>
@@ -1674,7 +1680,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:14" ht="30">
       <c r="A20" s="8">
         <v>46274</v>
       </c>
@@ -1718,7 +1724,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="1:14" ht="30">
       <c r="A21" s="8">
         <v>46275</v>
       </c>
@@ -1762,7 +1768,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:14" ht="30">
       <c r="A22" s="8">
         <v>46276</v>
       </c>
@@ -1850,7 +1856,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:14" ht="30">
       <c r="A24" s="8">
         <v>46278</v>
       </c>
@@ -1894,7 +1900,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:14" ht="30">
       <c r="A25" s="8">
         <v>46279</v>
       </c>
@@ -1938,7 +1944,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="1:14" ht="30">
       <c r="A26" s="8">
         <v>46280</v>
       </c>
@@ -1982,7 +1988,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="27" spans="1:14">
+    <row r="27" spans="1:14" ht="30">
       <c r="A27" s="8">
         <v>46281</v>
       </c>
@@ -2070,7 +2076,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="29" spans="1:14">
+    <row r="29" spans="1:14" ht="30">
       <c r="A29" s="8">
         <v>46283</v>
       </c>
@@ -2114,7 +2120,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="30" spans="1:14">
+    <row r="30" spans="1:14" ht="30">
       <c r="A30" s="8">
         <v>46284</v>
       </c>
@@ -2158,7 +2164,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="31" spans="1:14">
+    <row r="31" spans="1:14" ht="30">
       <c r="A31" s="8">
         <v>46285</v>
       </c>
@@ -2202,7 +2208,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="32" spans="1:14">
+    <row r="32" spans="1:14" ht="45">
       <c r="A32" s="8">
         <v>46286</v>
       </c>
@@ -2247,70 +2253,142 @@
       </c>
     </row>
     <row r="33" spans="1:14">
-      <c r="A33" s="8"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="10" t="str">
+      <c r="A33" s="8">
+        <v>46289</v>
+      </c>
+      <c r="B33" s="9">
+        <v>570</v>
+      </c>
+      <c r="C33" s="9">
+        <v>60</v>
+      </c>
+      <c r="D33" s="9">
+        <v>20</v>
+      </c>
+      <c r="E33" s="9">
+        <v>35</v>
+      </c>
+      <c r="F33" s="9">
+        <v>250</v>
+      </c>
+      <c r="G33" s="9">
+        <v>5</v>
+      </c>
+      <c r="H33" s="9">
+        <v>90</v>
+      </c>
+      <c r="I33" s="10">
         <f t="shared" ref="I33:I60" si="0">IF(SUM(B33:F33,H33)=0,"",SUM(B33:F33,H33))</f>
-        <v/>
-      </c>
-      <c r="J33" s="10" t="str">
+        <v>1025</v>
+      </c>
+      <c r="J33" s="10">
         <f t="shared" ref="J33:J60" si="1">IF(I33="","",1440-I33)</f>
-        <v/>
-      </c>
-      <c r="K33" s="11"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="11"/>
-      <c r="N33" s="12"/>
-    </row>
-    <row r="34" spans="1:14">
-      <c r="A34" s="8"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="10" t="str">
+        <v>415</v>
+      </c>
+      <c r="K33" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L33" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M33" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="N33" s="12" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" ht="30">
+      <c r="A34" s="8">
+        <v>46290</v>
+      </c>
+      <c r="B34" s="9">
+        <v>460</v>
+      </c>
+      <c r="C34" s="9">
+        <v>60</v>
+      </c>
+      <c r="D34" s="9">
+        <v>0</v>
+      </c>
+      <c r="E34" s="9">
+        <v>50</v>
+      </c>
+      <c r="F34" s="9">
+        <v>250</v>
+      </c>
+      <c r="G34" s="9">
+        <v>5</v>
+      </c>
+      <c r="H34" s="9">
+        <v>150</v>
+      </c>
+      <c r="I34" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="10" t="str">
+        <v>970</v>
+      </c>
+      <c r="J34" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="11"/>
-      <c r="L34" s="11"/>
-      <c r="M34" s="11"/>
-      <c r="N34" s="12"/>
+        <v>470</v>
+      </c>
+      <c r="K34" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L34" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M34" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N34" s="12" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="35" spans="1:14">
-      <c r="A35" s="8"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="10" t="str">
+      <c r="A35" s="8">
+        <v>46291</v>
+      </c>
+      <c r="B35" s="9">
+        <v>490</v>
+      </c>
+      <c r="C35" s="9">
+        <v>40</v>
+      </c>
+      <c r="D35" s="9">
+        <v>0</v>
+      </c>
+      <c r="E35" s="9">
+        <v>160</v>
+      </c>
+      <c r="F35" s="9">
+        <v>100</v>
+      </c>
+      <c r="G35" s="9">
+        <v>2</v>
+      </c>
+      <c r="H35" s="9">
+        <v>200</v>
+      </c>
+      <c r="I35" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="10" t="str">
+        <v>990</v>
+      </c>
+      <c r="J35" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="11"/>
-      <c r="L35" s="11"/>
-      <c r="M35" s="11"/>
-      <c r="N35" s="12"/>
+        <v>450</v>
+      </c>
+      <c r="K35" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L35" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M35" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N35" s="12" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="8"/>

--- a/12602999.xlsx
+++ b/12602999.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="93">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -307,6 +307,9 @@
   </si>
   <si>
     <t>tired after attendeing classes</t>
+  </si>
+  <si>
+    <t>college was off,followed protest updates through the social media</t>
   </si>
 </sst>
 </file>
@@ -2390,27 +2393,51 @@
         <v>90</v>
       </c>
     </row>
-    <row r="36" spans="1:14">
-      <c r="A36" s="8"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="10" t="str">
+    <row r="36" spans="1:14" ht="45">
+      <c r="A36" s="8">
+        <v>46292</v>
+      </c>
+      <c r="B36" s="9">
+        <v>550</v>
+      </c>
+      <c r="C36" s="9">
+        <v>50</v>
+      </c>
+      <c r="D36" s="9">
+        <v>0</v>
+      </c>
+      <c r="E36" s="9">
+        <v>130</v>
+      </c>
+      <c r="F36" s="9">
+        <v>0</v>
+      </c>
+      <c r="G36" s="9">
+        <v>0</v>
+      </c>
+      <c r="H36" s="9">
+        <v>200</v>
+      </c>
+      <c r="I36" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="10" t="str">
+        <v>930</v>
+      </c>
+      <c r="J36" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="11"/>
-      <c r="L36" s="11"/>
-      <c r="M36" s="11"/>
-      <c r="N36" s="12"/>
+        <v>510</v>
+      </c>
+      <c r="K36" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L36" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M36" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N36" s="12" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" s="8"/>

--- a/12602999.xlsx
+++ b/12602999.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="96">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -310,6 +310,15 @@
   </si>
   <si>
     <t>college was off,followed protest updates through the social media</t>
+  </si>
+  <si>
+    <t>travelled back to hometown due to college being off</t>
+  </si>
+  <si>
+    <t>spent the day at home and completed household and personal activities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spent the day at home </t>
   </si>
 </sst>
 </file>
@@ -2439,71 +2448,143 @@
         <v>92</v>
       </c>
     </row>
-    <row r="37" spans="1:14">
-      <c r="A37" s="8"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
-      <c r="I37" s="10" t="str">
+    <row r="37" spans="1:14" ht="30">
+      <c r="A37" s="8">
+        <v>46293</v>
+      </c>
+      <c r="B37" s="9">
+        <v>450</v>
+      </c>
+      <c r="C37" s="9">
+        <v>180</v>
+      </c>
+      <c r="D37" s="9">
+        <v>0</v>
+      </c>
+      <c r="E37" s="9">
+        <v>0</v>
+      </c>
+      <c r="F37" s="9">
+        <v>0</v>
+      </c>
+      <c r="G37" s="9">
+        <v>0</v>
+      </c>
+      <c r="H37" s="9">
+        <v>300</v>
+      </c>
+      <c r="I37" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="10" t="str">
+        <v>930</v>
+      </c>
+      <c r="J37" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="11"/>
-      <c r="L37" s="11"/>
-      <c r="M37" s="11"/>
-      <c r="N37" s="12"/>
-    </row>
-    <row r="38" spans="1:14">
-      <c r="A38" s="8"/>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="9"/>
-      <c r="I38" s="10" t="str">
+        <v>510</v>
+      </c>
+      <c r="K37" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L37" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M37" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N37" s="12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="45">
+      <c r="A38" s="8">
+        <v>46294</v>
+      </c>
+      <c r="B38" s="9">
+        <v>600</v>
+      </c>
+      <c r="C38" s="9">
+        <v>20</v>
+      </c>
+      <c r="D38" s="9">
+        <v>30</v>
+      </c>
+      <c r="E38" s="9">
+        <v>0</v>
+      </c>
+      <c r="F38" s="9">
+        <v>0</v>
+      </c>
+      <c r="G38" s="9">
+        <v>0</v>
+      </c>
+      <c r="H38" s="9">
+        <v>240</v>
+      </c>
+      <c r="I38" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="10" t="str">
+        <v>890</v>
+      </c>
+      <c r="J38" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="11"/>
-      <c r="L38" s="11"/>
-      <c r="M38" s="11"/>
-      <c r="N38" s="12"/>
+        <v>550</v>
+      </c>
+      <c r="K38" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L38" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M38" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="N38" s="12" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="39" spans="1:14">
-      <c r="A39" s="8"/>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
-      <c r="H39" s="9"/>
-      <c r="I39" s="10" t="str">
+      <c r="A39" s="8">
+        <v>46295</v>
+      </c>
+      <c r="B39" s="9">
+        <v>600</v>
+      </c>
+      <c r="C39" s="9">
+        <v>60</v>
+      </c>
+      <c r="D39" s="9">
+        <v>30</v>
+      </c>
+      <c r="E39" s="9">
+        <v>0</v>
+      </c>
+      <c r="F39" s="9">
+        <v>0</v>
+      </c>
+      <c r="G39" s="9">
+        <v>0</v>
+      </c>
+      <c r="H39" s="9">
+        <v>240</v>
+      </c>
+      <c r="I39" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="10" t="str">
+        <v>930</v>
+      </c>
+      <c r="J39" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="11"/>
-      <c r="L39" s="11"/>
-      <c r="M39" s="11"/>
-      <c r="N39" s="12"/>
+        <v>510</v>
+      </c>
+      <c r="K39" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L39" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M39" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="N39" s="12" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="8"/>

--- a/12602999.xlsx
+++ b/12602999.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="97">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -319,6 +319,9 @@
   </si>
   <si>
     <t xml:space="preserve">spent the day at home </t>
+  </si>
+  <si>
+    <t>relexed at home and done regular activities</t>
   </si>
 </sst>
 </file>
@@ -2586,27 +2589,51 @@
         <v>95</v>
       </c>
     </row>
-    <row r="40" spans="1:14">
-      <c r="A40" s="8"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="9"/>
-      <c r="I40" s="10" t="str">
+    <row r="40" spans="1:14" ht="30">
+      <c r="A40" s="8">
+        <v>46296</v>
+      </c>
+      <c r="B40" s="9">
+        <v>660</v>
+      </c>
+      <c r="C40" s="9">
+        <v>50</v>
+      </c>
+      <c r="D40" s="9">
+        <v>60</v>
+      </c>
+      <c r="E40" s="9">
+        <v>0</v>
+      </c>
+      <c r="F40" s="9">
+        <v>0</v>
+      </c>
+      <c r="G40" s="9">
+        <v>0</v>
+      </c>
+      <c r="H40" s="9">
+        <v>180</v>
+      </c>
+      <c r="I40" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="10" t="str">
+        <v>950</v>
+      </c>
+      <c r="J40" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="11"/>
-      <c r="L40" s="11"/>
-      <c r="M40" s="11"/>
-      <c r="N40" s="12"/>
+        <v>490</v>
+      </c>
+      <c r="K40" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L40" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M40" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="N40" s="12" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="8"/>

--- a/12602999.xlsx
+++ b/12602999.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="98">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -322,6 +322,9 @@
   </si>
   <si>
     <t>relexed at home and done regular activities</t>
+  </si>
+  <si>
+    <t>college was closed ,so was stayed at home and spend time on personal and household activity</t>
   </si>
 </sst>
 </file>
@@ -2635,27 +2638,51 @@
         <v>96</v>
       </c>
     </row>
-    <row r="41" spans="1:14">
-      <c r="A41" s="8"/>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
-      <c r="H41" s="9"/>
-      <c r="I41" s="10" t="str">
+    <row r="41" spans="1:14" ht="60">
+      <c r="A41" s="8">
+        <v>46297</v>
+      </c>
+      <c r="B41" s="9">
+        <v>660</v>
+      </c>
+      <c r="C41" s="9">
+        <v>40</v>
+      </c>
+      <c r="D41" s="9">
+        <v>0</v>
+      </c>
+      <c r="E41" s="9">
+        <v>30</v>
+      </c>
+      <c r="F41" s="9">
+        <v>0</v>
+      </c>
+      <c r="G41" s="9">
+        <v>0</v>
+      </c>
+      <c r="H41" s="9">
+        <v>300</v>
+      </c>
+      <c r="I41" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="10" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J41" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="11"/>
-      <c r="L41" s="11"/>
-      <c r="M41" s="11"/>
-      <c r="N41" s="12"/>
+        <v>410</v>
+      </c>
+      <c r="K41" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L41" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M41" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N41" s="12" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="8"/>

--- a/12602999.xlsx
+++ b/12602999.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="100">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -325,6 +325,12 @@
   </si>
   <si>
     <t>college was closed ,so was stayed at home and spend time on personal and household activity</t>
+  </si>
+  <si>
+    <t>attend demo class understand the setup,after that study for mids</t>
+  </si>
+  <si>
+    <t>relexed at home and prepared for the upcoming week</t>
   </si>
 </sst>
 </file>
@@ -2684,49 +2690,97 @@
         <v>97</v>
       </c>
     </row>
-    <row r="42" spans="1:14">
-      <c r="A42" s="8"/>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="9"/>
-      <c r="I42" s="10" t="str">
+    <row r="42" spans="1:14" ht="45">
+      <c r="A42" s="8">
+        <v>46298</v>
+      </c>
+      <c r="B42" s="9">
+        <v>530</v>
+      </c>
+      <c r="C42" s="9">
+        <v>60</v>
+      </c>
+      <c r="D42" s="9">
+        <v>300</v>
+      </c>
+      <c r="E42" s="9">
+        <v>0</v>
+      </c>
+      <c r="F42" s="9">
+        <v>0</v>
+      </c>
+      <c r="G42" s="9">
+        <v>0</v>
+      </c>
+      <c r="H42" s="9">
+        <v>200</v>
+      </c>
+      <c r="I42" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="10" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J42" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="11"/>
-      <c r="L42" s="11"/>
-      <c r="M42" s="11"/>
-      <c r="N42" s="12"/>
-    </row>
-    <row r="43" spans="1:14">
-      <c r="A43" s="8"/>
-      <c r="B43" s="9"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="9"/>
-      <c r="H43" s="9"/>
-      <c r="I43" s="10" t="str">
+        <v>350</v>
+      </c>
+      <c r="K42" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L42" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M42" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N42" s="12" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" ht="45">
+      <c r="A43" s="8">
+        <v>46299</v>
+      </c>
+      <c r="B43" s="9">
+        <v>570</v>
+      </c>
+      <c r="C43" s="9">
+        <v>40</v>
+      </c>
+      <c r="D43" s="9">
+        <v>120</v>
+      </c>
+      <c r="E43" s="9">
+        <v>30</v>
+      </c>
+      <c r="F43" s="9">
+        <v>0</v>
+      </c>
+      <c r="G43" s="9">
+        <v>0</v>
+      </c>
+      <c r="H43" s="9">
+        <v>150</v>
+      </c>
+      <c r="I43" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="10" t="str">
+        <v>910</v>
+      </c>
+      <c r="J43" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="11"/>
-      <c r="L43" s="11"/>
-      <c r="M43" s="11"/>
-      <c r="N43" s="12"/>
+        <v>530</v>
+      </c>
+      <c r="K43" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L43" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M43" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N43" s="12" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="8"/>

--- a/12602999.xlsx
+++ b/12602999.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="101">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -331,6 +331,9 @@
   </si>
   <si>
     <t>relexed at home and prepared for the upcoming week</t>
+  </si>
+  <si>
+    <t>attending online classes from home</t>
   </si>
 </sst>
 </file>
@@ -2782,27 +2785,51 @@
         <v>99</v>
       </c>
     </row>
-    <row r="44" spans="1:14">
-      <c r="A44" s="8"/>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="9"/>
-      <c r="H44" s="9"/>
-      <c r="I44" s="10" t="str">
+    <row r="44" spans="1:14" ht="30">
+      <c r="A44" s="8">
+        <v>46300</v>
+      </c>
+      <c r="B44" s="9">
+        <v>440</v>
+      </c>
+      <c r="C44" s="9">
+        <v>20</v>
+      </c>
+      <c r="D44" s="9">
+        <v>30</v>
+      </c>
+      <c r="E44" s="9">
+        <v>30</v>
+      </c>
+      <c r="F44" s="9">
+        <v>300</v>
+      </c>
+      <c r="G44" s="9">
+        <v>6</v>
+      </c>
+      <c r="H44" s="9">
+        <v>160</v>
+      </c>
+      <c r="I44" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="10" t="str">
+        <v>980</v>
+      </c>
+      <c r="J44" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="11"/>
-      <c r="L44" s="11"/>
-      <c r="M44" s="11"/>
-      <c r="N44" s="12"/>
+        <v>460</v>
+      </c>
+      <c r="K44" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L44" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M44" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N44" s="12" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="8"/>

--- a/12602999.xlsx
+++ b/12602999.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="102">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -334,6 +334,9 @@
   </si>
   <si>
     <t>attending online classes from home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tired after attendeing 8 online classes </t>
   </si>
 </sst>
 </file>
@@ -2831,27 +2834,51 @@
         <v>100</v>
       </c>
     </row>
-    <row r="45" spans="1:14">
-      <c r="A45" s="8"/>
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="9"/>
-      <c r="H45" s="9"/>
-      <c r="I45" s="10" t="str">
+    <row r="45" spans="1:14" ht="30">
+      <c r="A45" s="8">
+        <v>46302</v>
+      </c>
+      <c r="B45" s="9">
+        <v>490</v>
+      </c>
+      <c r="C45" s="9">
+        <v>20</v>
+      </c>
+      <c r="D45" s="9">
+        <v>30</v>
+      </c>
+      <c r="E45" s="9">
+        <v>0</v>
+      </c>
+      <c r="F45" s="9">
+        <v>400</v>
+      </c>
+      <c r="G45" s="9">
+        <v>8</v>
+      </c>
+      <c r="H45" s="9">
+        <v>120</v>
+      </c>
+      <c r="I45" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="10" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J45" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="11"/>
-      <c r="L45" s="11"/>
-      <c r="M45" s="11"/>
-      <c r="N45" s="12"/>
+        <v>380</v>
+      </c>
+      <c r="K45" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L45" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M45" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="N45" s="12" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="8"/>

--- a/12602999.xlsx
+++ b/12602999.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="103">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -337,6 +337,9 @@
   </si>
   <si>
     <t xml:space="preserve">tired after attendeing 8 online classes </t>
+  </si>
+  <si>
+    <t>attanded online workshop ,APTIMASTER</t>
   </si>
 </sst>
 </file>
@@ -2880,27 +2883,51 @@
         <v>101</v>
       </c>
     </row>
-    <row r="46" spans="1:14">
-      <c r="A46" s="8"/>
-      <c r="B46" s="9"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="9"/>
-      <c r="H46" s="9"/>
-      <c r="I46" s="10" t="str">
+    <row r="46" spans="1:14" ht="30">
+      <c r="A46" s="8">
+        <v>46303</v>
+      </c>
+      <c r="B46" s="9">
+        <v>500</v>
+      </c>
+      <c r="C46" s="9">
+        <v>60</v>
+      </c>
+      <c r="D46" s="9">
+        <v>30</v>
+      </c>
+      <c r="E46" s="9">
+        <v>0</v>
+      </c>
+      <c r="F46" s="9">
+        <v>0</v>
+      </c>
+      <c r="G46" s="9">
+        <v>0</v>
+      </c>
+      <c r="H46" s="9">
+        <v>160</v>
+      </c>
+      <c r="I46" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="10" t="str">
+        <v>750</v>
+      </c>
+      <c r="J46" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="11"/>
-      <c r="L46" s="11"/>
-      <c r="M46" s="11"/>
-      <c r="N46" s="12"/>
+        <v>690</v>
+      </c>
+      <c r="K46" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L46" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M46" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N46" s="12" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="8"/>

--- a/12602999.xlsx
+++ b/12602999.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="105">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -340,6 +340,12 @@
   </si>
   <si>
     <t>attanded online workshop ,APTIMASTER</t>
+  </si>
+  <si>
+    <t>prepare for mids</t>
+  </si>
+  <si>
+    <t>trevel from home and settled back into my room</t>
   </si>
 </sst>
 </file>
@@ -2929,49 +2935,97 @@
         <v>102</v>
       </c>
     </row>
-    <row r="47" spans="1:14">
-      <c r="A47" s="8"/>
-      <c r="B47" s="9"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="9"/>
-      <c r="E47" s="9"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="9"/>
-      <c r="H47" s="9"/>
-      <c r="I47" s="10" t="str">
+    <row r="47" spans="1:14" ht="30">
+      <c r="A47" s="8">
+        <v>46305</v>
+      </c>
+      <c r="B47" s="9">
+        <v>360</v>
+      </c>
+      <c r="C47" s="9">
+        <v>190</v>
+      </c>
+      <c r="D47" s="9">
+        <v>0</v>
+      </c>
+      <c r="E47" s="9">
+        <v>0</v>
+      </c>
+      <c r="F47" s="9">
+        <v>0</v>
+      </c>
+      <c r="G47" s="9">
+        <v>0</v>
+      </c>
+      <c r="H47" s="9">
+        <v>300</v>
+      </c>
+      <c r="I47" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="10" t="str">
+        <v>850</v>
+      </c>
+      <c r="J47" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="11"/>
-      <c r="L47" s="11"/>
-      <c r="M47" s="11"/>
-      <c r="N47" s="12"/>
+        <v>590</v>
+      </c>
+      <c r="K47" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="L47" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M47" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="N47" s="12" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="48" spans="1:14">
-      <c r="A48" s="8"/>
-      <c r="B48" s="9"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="9"/>
-      <c r="H48" s="9"/>
-      <c r="I48" s="10" t="str">
+      <c r="A48" s="8">
+        <v>46306</v>
+      </c>
+      <c r="B48" s="9">
+        <v>440</v>
+      </c>
+      <c r="C48" s="9">
+        <v>90</v>
+      </c>
+      <c r="D48" s="9">
+        <v>120</v>
+      </c>
+      <c r="E48" s="9">
+        <v>0</v>
+      </c>
+      <c r="F48" s="9">
+        <v>0</v>
+      </c>
+      <c r="G48" s="9">
+        <v>0</v>
+      </c>
+      <c r="H48" s="9">
+        <v>360</v>
+      </c>
+      <c r="I48" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="10" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J48" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="11"/>
-      <c r="L48" s="11"/>
-      <c r="M48" s="11"/>
-      <c r="N48" s="12"/>
+        <v>430</v>
+      </c>
+      <c r="K48" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L48" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M48" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N48" s="12" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="49" spans="1:14">
       <c r="A49" s="8"/>
